--- a/results/Int All Data -0.7/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.7/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.000535490994269504</v>
+        <v>0.00116585250937457</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004338805830291337</v>
+        <v>0.0006531672902592566</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0005325922823972452</v>
+        <v>0.0001306811864796498</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0003530514469834312</v>
+        <v>9.184054785576052e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.107567752225202e-05</v>
+        <v>-7.670449424136965e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00183376686543025</v>
+        <v>0.001332767626224789</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0001134588842886741</v>
+        <v>0.0001253575238908954</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0004385103404645008</v>
+        <v>-0.0001284999386632235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0005916784860786749</v>
+        <v>-0.001444329682022293</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001421453481733726</v>
+        <v>5.742547980595704e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-9.491117089932998e-05</v>
+        <v>-0.0001375268552750775</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0006010507828332278</v>
+        <v>-0.0008068953351249441</v>
       </c>
       <c r="N3" t="n">
-        <v>0.001274440865292028</v>
+        <v>0.001089806080914938</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.001297177587541532</v>
+        <v>-0.0005950607435848876</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.419985226112862e-06</v>
+        <v>0.0006860381587371167</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004696756873067085</v>
+        <v>0.003898750344864361</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.000650091261022092</v>
+        <v>0.0005346790772824239</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0004093906762845889</v>
+        <v>-0.0004316560420588956</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0005307678739603384</v>
+        <v>6.490616394468684e-05</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002526606542304167</v>
+        <v>0.0007342938634713991</v>
       </c>
       <c r="V3" t="n">
-        <v>0.000622063221662642</v>
+        <v>-0.0004406851898384313</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0005322400928586646</v>
+        <v>-0.0005824788065232845</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0001470252139857021</v>
+        <v>-0.0001882277096011686</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0007181441250986652</v>
+        <v>-6.330804444488302e-05</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0002896698643204653</v>
+        <v>0.0002084432716861207</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.004546071364377227</v>
+        <v>0.002678535276957038</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0003338568868882119</v>
+        <v>0.0001331898503243512</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0002398891524182634</v>
+        <v>-0.001338216949167617</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.005348264378494418</v>
+        <v>0.005095659748732715</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.008174360686751234</v>
+        <v>0.004998255496358048</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.002162449431891089</v>
+        <v>0.001336619062812066</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0001944231492115001</v>
+        <v>-0.0003048212100098368</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001448239106801608</v>
+        <v>-0.0003594597037053393</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.001695662572835082</v>
+        <v>0.0003992207736264786</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.004739426648488598</v>
+        <v>0.001636909569449703</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01613369286829453</v>
+        <v>0.01003615839131309</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.0007607345330007798</v>
+        <v>-0.001008809966154672</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.002987059918608</v>
+        <v>0.002846842315205406</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0004858642099117882</v>
+        <v>-0.0004355944705609559</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001511527608368759</v>
+        <v>-0.0003523534803252314</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0001917019229025651</v>
+        <v>-0.0006776757878512441</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001041807029488905</v>
+        <v>0.001559813035840322</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.01016101019856979</v>
+        <v>0.006435684497885086</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.084874434061582e-05</v>
+        <v>-5.990525975363422e-05</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.000273392208690353</v>
+        <v>-2.214473191374362e-05</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.000751625231639671</v>
+        <v>-0.0007637923684892399</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0003514040019898312</v>
+        <v>0.0002694403935362588</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.001293639273413442</v>
+        <v>-0.001129640259325055</v>
       </c>
       <c r="AX3" t="n">
-        <v>-9.215296222454869e-05</v>
+        <v>7.006760236597743e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0006324855560826126</v>
+        <v>0.001678292577238665</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001736440868494272</v>
+        <v>0.0004526810679679472</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.003569753206119952</v>
+        <v>-0.0001145005820469713</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0006369421623368931</v>
+        <v>-0.0001949513427172668</v>
       </c>
       <c r="BC3" t="n">
-        <v>-4.313292951180214e-05</v>
+        <v>-5.883544725483469e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.933039080002425e-05</v>
+        <v>2.39646175209851e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0004526608651488658</v>
+        <v>0.0001121690060011872</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001164216588678543</v>
+        <v>0.001016217824158012</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0003331814409228951</v>
+        <v>-0.0008940184202131107</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0001579325425072575</v>
+        <v>0.0002480348928595065</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.005398963755756543</v>
+        <v>0.004255155679695204</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0004752701294936878</v>
+        <v>0.001488643602029159</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.0003581646346587664</v>
+        <v>-4.940771774146089e-05</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0003468861030988002</v>
+        <v>-0.000380129916136579</v>
       </c>
       <c r="BM3" t="n">
-        <v>-3.529148685218588e-05</v>
+        <v>-0.001010445412987792</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.001299319164480373</v>
+        <v>0.0003746077303852679</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001519588444081891</v>
+        <v>0.0008412989934835968</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.000482543053880331</v>
+        <v>-0.000793043007809784</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>2.761456861489436e-05</v>
+        <v>0.0004548579542224873</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0004647347045712214</v>
+        <v>-0.0009580580511551783</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0001318925037414453</v>
+        <v>0.001222065287516148</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.707947818928911e-05</v>
+        <v>0.000850346855733607</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0006554490677042645</v>
+        <v>-0.0007940943164789427</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.686849253113357e-05</v>
+        <v>2.120065840044538e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.0004679706316320142</v>
+        <v>-0.0007524682098029801</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.001384045452811836</v>
+        <v>0.0003112211402977694</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.0005785468785140068</v>
+        <v>-0.0002947066018201649</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0004898205430634517</v>
+        <v>0.0003971689582319216</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001609162184422852</v>
+        <v>-0.0002070996364389455</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0005392974054777877</v>
+        <v>0.0007961274625762083</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.000405743287288144</v>
+        <v>-0.0004328905867326272</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0005630084730426511</v>
+        <v>-0.002720016793602065</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.468157278059165e-05</v>
+        <v>-3.618635881606156e-05</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0004780137263724049</v>
+        <v>0.0001326349501706114</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0002010169339681467</v>
+        <v>-0.0002013930210075898</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.001291436435980919</v>
+        <v>-0.0006164333105979381</v>
       </c>
       <c r="CJ3" t="n">
-        <v>6.514646249146105e-06</v>
+        <v>-9.163084908935247e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.000156780405029342</v>
+        <v>-0.0005518424769923059</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.002033013694593811</v>
+        <v>-0.002480124345602642</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001164426959627366</v>
+        <v>0.0005773565706407569</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.0005923545038840373</v>
+        <v>0.0006239450697231996</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.001273386720183965</v>
+        <v>0.00072848515664383</v>
       </c>
       <c r="CP3" t="n">
-        <v>-8.388051299846883e-06</v>
+        <v>0.0001815232514283294</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001101490930899735</v>
+        <v>0.0009153596014580179</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001394984781186173</v>
+        <v>-0.002319434799579656</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.001393427058376947</v>
+        <v>-0.0009587516144541668</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.002619037934442182</v>
+        <v>-0.003139636114270955</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0001716426109062486</v>
+        <v>8.147695081371696e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0002031217118746998</v>
+        <v>0.0001017512840299539</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.002606320836054454</v>
+        <v>-0.003984270949902322</v>
       </c>
       <c r="CY3" t="n">
-        <v>-0.0008909657653475754</v>
+        <v>-0.002106850407280411</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.0001052411515868423</v>
+        <v>-9.320715586944362e-05</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0003416321170537717</v>
+        <v>0.0002609785624783856</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001117047854908313</v>
+        <v>-0.0003727048625501206</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.0008552936255847444</v>
+        <v>-0.001937818394743907</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.0001100973228627655</v>
+        <v>5.51061540184028e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0005819950452059507</v>
+        <v>0.0008242043077266037</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.001544588266860819</v>
+        <v>-0.002984413260169298</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.756507698696868e-06</v>
+        <v>0.001081068353898747</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001377718428122109</v>
+        <v>-0.001377758944356121</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.0002107022019115279</v>
+        <v>-0.0007517486685837892</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.0002556449769995828</v>
+        <v>0.0005626719710254769</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0009121882997229092</v>
+        <v>-0.001456585711134565</v>
       </c>
       <c r="DL3" t="n">
-        <v>-9.728019521042963e-05</v>
+        <v>0.0001116852371445987</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0003446590999543053</v>
+        <v>-9.179289826945606e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0009548874156757849</v>
+        <v>-0.0005114447119429544</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.002426926743665526</v>
+        <v>-0.0001682123783290778</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.001544902482693817</v>
+        <v>-0.0002645251016845085</v>
       </c>
       <c r="DQ3" t="n">
-        <v>3.056006386739973e-05</v>
+        <v>-9.186313485429421e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>-5.394513804137802e-05</v>
+        <v>-2.331990129376905e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-6.717148936676861e-06</v>
+        <v>-1.066375582719158e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.0004576462528234049</v>
+        <v>-0.0003565589734314489</v>
       </c>
       <c r="DU3" t="n">
-        <v>7.442108222303182e-05</v>
+        <v>-0.00033922095034422</v>
       </c>
       <c r="DV3" t="n">
-        <v>-7.52115324349778e-05</v>
+        <v>2.93850974181109e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001569356007742084</v>
+        <v>0.0003449556246570596</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.0003774996446919066</v>
+        <v>0.0003223111439580695</v>
       </c>
       <c r="DY3" t="n">
-        <v>6.323911848470695e-05</v>
+        <v>-0.001239173627464316</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0004653172442221265</v>
+        <v>0.0005108901667745115</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0007260802458314332</v>
+        <v>-0.0008489247612465566</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.002652614105496348</v>
+        <v>-0.0009161674884061542</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0001357007656997311</v>
+        <v>6.562360295580885e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>-8.969144439040619e-05</v>
+        <v>-0.0003618342090751359</v>
       </c>
       <c r="EE3" t="n">
-        <v>6.788723835085664e-05</v>
+        <v>1.716643175099231e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0002371498686545337</v>
+        <v>-0.0006919779371577561</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0003028987078260414</v>
+        <v>-7.975503588263711e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>-7.883157824137399e-05</v>
+        <v>0.0001417538954172226</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.001596466825757156</v>
+        <v>-8.626768857734395e-05</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0006087833098359319</v>
+        <v>-0.000288615483774326</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0001619248881737656</v>
+        <v>0.0002651608166044595</v>
       </c>
       <c r="EL3" t="n">
-        <v>2.978911656815741e-06</v>
+        <v>-1.873795541840199e-07</v>
       </c>
       <c r="EM3" t="n">
-        <v>-7.815680654046364e-05</v>
+        <v>-0.0001421280069552844</v>
       </c>
       <c r="EN3" t="n">
-        <v>-3.172237166419345e-05</v>
+        <v>-2.569017741848034e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>2.592912705272954e-05</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>1.655429710675892e-05</v>
+        <v>8.46956862481507e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0003061012257166229</v>
+        <v>-0.0002792794595402626</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.0002092327844100284</v>
+        <v>-3.164031916640053e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.0001170104918962766</v>
+        <v>5.843790391223625e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.0006190225116933978</v>
+        <v>8.256988551226806e-05</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.0002175374058528634</v>
+        <v>-0.001049984815337594</v>
       </c>
       <c r="EV3" t="n">
-        <v>-7.119838555448278e-06</v>
+        <v>5.920857502768051e-05</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.000479468052759705</v>
+        <v>0.0001771446332498217</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0002486401800396732</v>
+        <v>0.000368197480623037</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0003974917189361205</v>
+        <v>5.829155021428453e-06</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002621906252154661</v>
+        <v>0.002329096219363912</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0009314745374783157</v>
+        <v>0.001915318039649472</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001121228499521873</v>
+        <v>0.001082652556541418</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001401544498563372</v>
+        <v>0.002005658476687936</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001022199158958691</v>
+        <v>0.001315671538752327</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003673771423513843</v>
+        <v>0.004471471204971801</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001810698711347749</v>
+        <v>0.002133945437930171</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005895496446629138</v>
+        <v>0.00321403764568133</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002521456206969034</v>
+        <v>0.001810052804584213</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006491035404513954</v>
+        <v>0.0006946987823568782</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005895635653277464</v>
+        <v>0.0008517395259082266</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001369596064826103</v>
+        <v>0.001861046947824139</v>
       </c>
       <c r="N4" t="n">
-        <v>0.007274546798123587</v>
+        <v>0.004594621276540542</v>
       </c>
       <c r="O4" t="n">
-        <v>0.005521600026182567</v>
+        <v>0.002120078636693385</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001312754273390958</v>
+        <v>0.002731796285830038</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.007013061596122013</v>
+        <v>0.00804335637160305</v>
       </c>
       <c r="R4" t="n">
-        <v>0.003786107371639954</v>
+        <v>0.001237056643660993</v>
       </c>
       <c r="S4" t="n">
-        <v>0.004675204633688432</v>
+        <v>0.002077586709725741</v>
       </c>
       <c r="T4" t="n">
-        <v>0.00108930900774732</v>
+        <v>0.0009241417407805159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001373528857305169</v>
+        <v>0.001267387184437493</v>
       </c>
       <c r="V4" t="n">
-        <v>0.007055809789327187</v>
+        <v>0.002915004317136281</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0007912882515241487</v>
+        <v>0.001840026766531569</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004419179671036848</v>
+        <v>0.003315916321497568</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.001742558881902044</v>
+        <v>0.001052842096227842</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.003843289197589133</v>
+        <v>0.002104380993904633</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.004997781524662985</v>
+        <v>0.004605556992764777</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0005853998201208048</v>
+        <v>0.0005801401212961844</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002678520306391427</v>
+        <v>0.002087664388711366</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.003438796382760608</v>
+        <v>0.004318912231771116</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.007210199348519266</v>
+        <v>0.005960382108314699</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002527291869835344</v>
+        <v>0.002329494285754163</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001679050235112671</v>
+        <v>0.001046669745080106</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001073380316011465</v>
+        <v>0.001439959917411626</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.002771960946435271</v>
+        <v>0.0009483396510710548</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.00691231228676655</v>
+        <v>0.005780190726253583</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0133741791839366</v>
+        <v>0.007362136828444263</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001463632676449064</v>
+        <v>0.001202729948796172</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.004446736181794374</v>
+        <v>0.005394135537120346</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.001910151134407432</v>
+        <v>0.003196221179396573</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.00347748587609599</v>
+        <v>0.004132188641969522</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001474183934959927</v>
+        <v>0.001768602564747723</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.004435573076992735</v>
+        <v>0.004964701486030045</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.007645093624847418</v>
+        <v>0.005623326855496333</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.001205885681334698</v>
+        <v>0.001511679113581584</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003130257026502493</v>
+        <v>0.002456309229729903</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001384406754810876</v>
+        <v>0.003509620900087661</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001046001064983769</v>
+        <v>0.001617375757492697</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002572248114986886</v>
+        <v>0.002497885821320066</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.00104772312173081</v>
+        <v>0.0007715922712132243</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001771811704427795</v>
+        <v>0.002990602730937653</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004071721023627568</v>
+        <v>0.002105993403388607</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.007383165132015359</v>
+        <v>0.003278540054828435</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004240870034835727</v>
+        <v>0.004775034730465258</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0004588173419839309</v>
+        <v>0.0005646625220022576</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0002857243984173659</v>
+        <v>0.00110352178515224</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004023891421317295</v>
+        <v>0.002913752064656703</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.002640048543829981</v>
+        <v>0.005518168697838233</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004009891502959582</v>
+        <v>0.002139377011318241</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0007620077758079633</v>
+        <v>0.001560859659392419</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00749048600098531</v>
+        <v>0.00589728736730176</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001617837760899574</v>
+        <v>0.002294516817731258</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002662555985247505</v>
+        <v>0.002472201664174866</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001054430451911919</v>
+        <v>0.001420547530656296</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001584677085892109</v>
+        <v>0.001939720041599772</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.003863184284979652</v>
+        <v>0.003998965819661273</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.006596947276575025</v>
+        <v>0.003013992985377372</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.001722340868323186</v>
+        <v>0.002242165184440692</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.002456669782442566</v>
+        <v>0.002455677315963455</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.001854967827492068</v>
+        <v>0.001509887153248676</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.001327710846540834</v>
+        <v>0.001879581120379543</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.002110666592199649</v>
+        <v>0.002478543797662082</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002492470936084956</v>
+        <v>0.001318060366368955</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001277089713268573</v>
+        <v>2.498338021330268e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.002510341263018922</v>
+        <v>0.002150141893945138</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.004319093496891247</v>
+        <v>0.002108802964599698</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.004163387362772333</v>
+        <v>0.002738199247382145</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001423899789799999</v>
+        <v>0.001616928034218151</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001769892123597928</v>
+        <v>0.001871732490606465</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.001892563941878362</v>
+        <v>0.003179212713088042</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001796678795488906</v>
+        <v>0.002909767266787715</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.003319628117169379</v>
+        <v>0.005120032670000105</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001849639171218614</v>
+        <v>0.001552325192755853</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001898731658698099</v>
+        <v>0.003473030310958585</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001464564059864783</v>
+        <v>0.001471763831719117</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.002684285228903807</v>
+        <v>0.002423817250632477</v>
       </c>
       <c r="CJ4" t="n">
-        <v>7.014618003816629e-05</v>
+        <v>4.750704385332146e-05</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001894375286787282</v>
+        <v>0.001675752526922694</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.005415435669652475</v>
+        <v>0.006079230535984679</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001275342569271711</v>
+        <v>0.001177960412318653</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001063802758950749</v>
+        <v>0.0009224172309108931</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001567530591622061</v>
+        <v>0.001766453525715927</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0003354918340217236</v>
+        <v>0.0003581045892181698</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002222763302573112</v>
+        <v>0.003975256173976725</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.009349752227880303</v>
+        <v>0.004629186730449629</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.004281712698071432</v>
+        <v>0.003795359248364831</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.007426046377749342</v>
+        <v>0.006848917603103107</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0004453903291696165</v>
+        <v>0.0002923009701645154</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.000348952744615536</v>
+        <v>0.0003170004261823543</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.006767966794103297</v>
+        <v>0.008396125450209888</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.006402992146275378</v>
+        <v>0.004129641353067238</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0007521158050900143</v>
+        <v>0.0006297941744420136</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0006163700220703842</v>
+        <v>0.0003836999384884817</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.002143717391944278</v>
+        <v>0.001839902574416177</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.003267201977867743</v>
+        <v>0.005585164655823962</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.000255178107218238</v>
+        <v>0.0004320771529509614</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.002112852990442532</v>
+        <v>0.00378759780117038</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.004890435894300034</v>
+        <v>0.007371672053820113</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.001136205932496316</v>
+        <v>0.002792165213657127</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.003234372631611607</v>
+        <v>0.002612145322582092</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001968689478522679</v>
+        <v>0.001954913453136664</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002376853883446901</v>
+        <v>0.001397628432052175</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.004358004689327823</v>
+        <v>0.00397472013515699</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0005451689569490046</v>
+        <v>0.0003341169047799796</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.00166206077005854</v>
+        <v>0.000632130406986531</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.00319546229719114</v>
+        <v>0.001586985125114057</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004055928977089869</v>
+        <v>0.002003247366519778</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.002152421405986724</v>
+        <v>0.002477508341390328</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0004053862379616425</v>
+        <v>0.0003650916452104951</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0003558205998024205</v>
+        <v>0.0002923816432864559</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0001791891709247314</v>
+        <v>0.0003933720437593154</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.002187287642303778</v>
+        <v>0.002118938141543217</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.001105667017675483</v>
+        <v>0.002244856200250658</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.0002378397488061598</v>
+        <v>2.177687004208458e-05</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0005091142966113641</v>
+        <v>0.0007630569820880772</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.0008721488818896678</v>
+        <v>0.0006201368379121184</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.002521545391220403</v>
+        <v>0.001454270272479165</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0006198716258552372</v>
+        <v>0.0006007735591698442</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002881621181828945</v>
+        <v>0.004219501923379261</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.005714981824635736</v>
+        <v>0.002444906501605396</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.000938805133182521</v>
+        <v>0.001640950085561166</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.0007605126614652249</v>
+        <v>0.001058065903311519</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001775277562152572</v>
+        <v>0.000123714235432923</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001854133953061132</v>
+        <v>0.001373964259638354</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001858654049538161</v>
+        <v>0.0006595267442257382</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0005222664064276027</v>
+        <v>0.0003415078708737145</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002415079449355418</v>
+        <v>0.001235181699797165</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.0008371676360858429</v>
+        <v>0.0006844836555585936</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001385177403305818</v>
+        <v>0.001480041700937736</v>
       </c>
       <c r="EL4" t="n">
-        <v>2.948282182731448e-05</v>
+        <v>5.051534109941421e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0001828499690370944</v>
+        <v>0.0003839345768760661</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001669022714483024</v>
+        <v>0.0002500407737549407</v>
       </c>
       <c r="EO4" t="n">
-        <v>8.199509922651418e-05</v>
+        <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0009261989521804793</v>
+        <v>0.000296412759111182</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001032892937040043</v>
+        <v>0.001341727337930801</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0007677832511074793</v>
+        <v>0.0001135360755814197</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0003138439634739651</v>
+        <v>0.0002500426481930358</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.00153132989432085</v>
+        <v>0.0009189902155740639</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001383487001408971</v>
+        <v>0.002201793842006596</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0003456302931744287</v>
+        <v>0.0002508268608279968</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001193499979827297</v>
+        <v>0.001810031443047842</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001086445208419385</v>
+        <v>0.001312665310301908</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.0006291226581816812</v>
+        <v>0.0005960457613722402</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003973105134474286</v>
+        <v>-0.001657785671995238</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0009518143961927516</v>
+        <v>-0.001427721594289144</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.003566165635131124</v>
+        <v>-0.001546698393813239</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.002309058614564796</v>
+        <v>-0.002801533470952478</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.002498512790005947</v>
+        <v>-0.002215288611544464</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.001183782184078197</v>
+        <v>-0.004892425582080706</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.003422982885085535</v>
+        <v>-0.002736466389054193</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01201100244498774</v>
+        <v>-0.005658709106984916</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.003509871513632123</v>
+        <v>-0.004149765990639609</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0008328375966686674</v>
+        <v>-0.000981558596073817</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.001011302795954805</v>
+        <v>-0.00227769110764432</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003270171149144208</v>
+        <v>-0.004461629982153525</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.006081907090464489</v>
+        <v>-0.006552262090483619</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01555623471882634</v>
+        <v>-0.00430297671676978</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.002156573116691274</v>
+        <v>-0.002249851983422113</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.005658709106984938</v>
+        <v>-0.006041850869437038</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01020782396088016</v>
+        <v>-0.0007368110816386331</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.01228606356968212</v>
+        <v>-0.003948605452836118</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.000680674755845001</v>
+        <v>-0.0009220701963117639</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0008846947803008542</v>
+        <v>-0.001069682151589268</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01742053789731045</v>
+        <v>-0.006778661951075704</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0006778661951075571</v>
+        <v>-0.003107428233205056</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.008496332518337379</v>
+        <v>-0.00651725154821583</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.005417406749555908</v>
+        <v>-0.002723505032563622</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.007724178751109856</v>
+        <v>-0.004320804971885172</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.001065975223278537</v>
+        <v>-0.00199687987519499</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.00064180929095351</v>
+        <v>-0.0007667354762606494</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.003514669926650316</v>
+        <v>-0.004675939627108628</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.0001179593040401716</v>
+        <v>-0.0002960331557134155</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.002658924205378943</v>
+        <v>-0.002914446881855259</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001154187629476233</v>
+        <v>-0.00429248075784483</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.002870671796389523</v>
+        <v>-0.001538916839301541</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001827291482463866</v>
+        <v>-0.002736466389054182</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001503094606542854</v>
+        <v>-0.0008643042350907293</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.003102475712942676</v>
+        <v>-0.01043560012535258</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.004313146233382548</v>
+        <v>0.002067946824224509</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.004015466983938132</v>
+        <v>-0.002978472427012613</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.004450015669069285</v>
+        <v>-0.004232021308079337</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.001933372992266513</v>
+        <v>-0.008935417281037982</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.007701711491442498</v>
+        <v>-0.01041728321988756</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.002362431575914681</v>
+        <v>-0.00340093603744146</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.006984969053934542</v>
+        <v>-0.005304212168486722</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.001686889612311304</v>
+        <v>-0.002308375258952355</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002392909896602646</v>
+        <v>-0.00296411856474259</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.00663202933985324</v>
+        <v>-0.004680187207488274</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001096834848010075</v>
+        <v>-0.0100355239786856</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.001642178046672371</v>
+        <v>-0.002068317141961773</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.005959657701711451</v>
+        <v>-0.00698638247483716</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001856763925729399</v>
+        <v>-0.001035809411068345</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.0006483937518420024</v>
+        <v>-0.00248594258656405</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.00767114914425423</v>
+        <v>-0.004430577223088916</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.003876886652855916</v>
+        <v>-0.005366614664586556</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.007018578590386371</v>
+        <v>-0.008787968150987835</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0007696862048549135</v>
+        <v>-0.0009360374414976502</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.000374531835205949</v>
+        <v>-0.0027145085803432</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.00716602772043653</v>
+        <v>-0.006510802012429706</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.001996879875195001</v>
+        <v>-0.01135725429017158</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01139975550122245</v>
+        <v>-0.004798288508557502</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.0008251833740830939</v>
+        <v>-0.001828369212621605</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.003899556868537646</v>
+        <v>-0.001595273264401764</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001035809411068434</v>
+        <v>-0.001341653666146614</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.007396088019559844</v>
+        <v>-0.003155411383072781</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001242971293282125</v>
+        <v>-0.003955978584176156</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.002161042036708072</v>
+        <v>-0.004825340438129056</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.003911980440097762</v>
+        <v>-0.006739469578783119</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006483937518420258</v>
+        <v>-0.003759621077560671</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.003866745984533004</v>
+        <v>-0.00615748963883952</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.002865583456425391</v>
+        <v>-0.003307332293291709</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002475550122249337</v>
+        <v>-0.003966844286560078</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001546698393813228</v>
+        <v>-0.001568511393903516</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.003630077787381103</v>
+        <v>-0.003213728549141925</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.006008328375966687</v>
+        <v>-0.002516281823564215</v>
       </c>
       <c r="BW5" t="n">
-        <v>-6.112469437651314e-05</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.004064792176039089</v>
+        <v>-0.006039076376554165</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.007640586797065985</v>
+        <v>-0.001974302726418076</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003699319325244199</v>
+        <v>-0.006364712847838927</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.001562960778531475</v>
+        <v>-0.002005640864932634</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.001861152141802058</v>
+        <v>-0.002575488454706898</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001786228752520835</v>
+        <v>-0.005150976909413829</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.00327186198691255</v>
+        <v>-0.007430432208407322</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.007134399052693885</v>
+        <v>-0.01554174067495557</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.001532567049808375</v>
+        <v>-0.002464898595943821</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003697900344719551</v>
+        <v>-0.007104795737122538</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002623047450633631</v>
+        <v>-0.002647233789411119</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.005891059798697418</v>
+        <v>-0.005429017160686412</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0001480165778566911</v>
+        <v>-9.401441554370837e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.002604320804971949</v>
+        <v>-0.003447195236602951</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.01592658377738305</v>
+        <v>-0.01835405565423325</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.0001772525849335294</v>
+        <v>-0.0009174311926605338</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001479727730097724</v>
+        <v>-0.001338488994646081</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.0009174311926606005</v>
+        <v>-0.001272565847883966</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0005918910920391541</v>
+        <v>-0.0002444987775061413</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.004409588635691064</v>
+        <v>-0.004118564742589692</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.02534043812907043</v>
+        <v>-0.01187092954410891</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.01352871521610418</v>
+        <v>-0.01071640023682651</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.02341622261693306</v>
+        <v>-0.01897572528123146</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0004759071980963592</v>
+        <v>-0.0003551346552234325</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0003169115528665723</v>
+        <v>-0.0003457216940362607</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.02140319715808166</v>
+        <v>-0.0263173475429248</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.01767317939609232</v>
+        <v>-0.01201894612196563</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.001955990220048864</v>
+        <v>-0.0006782659982305872</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0005640864932623613</v>
+        <v>-0.0002663509914175743</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.002900266350991476</v>
+        <v>-0.002974419988102384</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.008259325044404931</v>
+        <v>-0.01675547661338066</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0001880288310874834</v>
+        <v>-0.0008923259964307428</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.004320804971885217</v>
+        <v>-0.002870671796389468</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01423919478981642</v>
+        <v>-0.02294256956779158</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.001450133175495794</v>
+        <v>-0.001466992665036704</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01033155713439902</v>
+        <v>-0.006753170156296051</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.002794583693460051</v>
+        <v>-0.005367148333824789</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.004391394046566422</v>
+        <v>-0.001248049921996886</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.01320365458296492</v>
+        <v>-0.01258473327438839</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.001427721594289122</v>
+        <v>-0.000374531835205949</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.002108801955990169</v>
+        <v>-0.001123244929797185</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.007134399052693874</v>
+        <v>-0.002349791790600908</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01249999999999997</v>
+        <v>-0.00322676139727649</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.006009473060982806</v>
+        <v>-0.00568383658969801</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0009174311926606448</v>
+        <v>-0.0007957559681696979</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0009141846063108972</v>
+        <v>-0.0005327483547477585</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0003271861986912317</v>
+        <v>-0.0007104795737122415</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.004372397382510407</v>
+        <v>-0.003745207903273318</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.002569727358194962</v>
+        <v>-0.00424653494544378</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0.000752115324349778</v>
+        <v>-2.959455460195271e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0008841732979663952</v>
+        <v>-0.0007202535292422429</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.002200488997554984</v>
+        <v>-0.000280811232449274</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.002239905688181532</v>
+        <v>-0.003745207903273318</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.000218408736349418</v>
+        <v>-0.0002368265245707657</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.008429118773946332</v>
+        <v>-0.01243737105806068</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.0177915926583777</v>
+        <v>-0.005927455028015294</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.001506646971934999</v>
+        <v>-0.002506635210852215</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.0010904804008252</v>
+        <v>-0.0029177718832891</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0.0002652519893898919</v>
+        <v>-0.0001833740831296171</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.005010315355142925</v>
+        <v>-0.00391983495431768</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.004804008252284076</v>
+        <v>-0.001296787503683994</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.001444149720011767</v>
+        <v>-0.0001560062402495843</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.007397583259652174</v>
+        <v>-0.002888299440023534</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.001797819039198312</v>
+        <v>-0.001566906925728639</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.002256345973049256</v>
+        <v>-0.003420582986317744</v>
       </c>
       <c r="EL5" t="n">
-        <v>-5.918910920390541e-05</v>
+        <v>-6.267627702913892e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0003538779121203706</v>
+        <v>-0.001216848673946957</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0003271861986912317</v>
+        <v>-0.0003552397868561319</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.001497555012224894</v>
+        <v>-0.000503107428233196</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002328323017978162</v>
+        <v>-0.003330386089006732</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.002387267904509249</v>
+        <v>-0.000324196875920979</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0002357795461243373</v>
+        <v>-0.0004700720777185863</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.004332449160035346</v>
+        <v>-0.001420959147424494</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.001034158570980914</v>
+        <v>-0.006896551724137867</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0006483937518420024</v>
+        <v>-0.0003447195236602974</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.003507220748600037</v>
+        <v>-0.004155614500442051</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.001959089599538977</v>
+        <v>-0.002092543471853769</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001986552567237132</v>
+        <v>-0.0007957559681697202</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.001964553591829801</v>
+        <v>-0.0003423675459982289</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0003100083693863997</v>
+        <v>-0.0001728608470181192</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0004928843176854436</v>
+        <v>-0.0003631156482213959</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.001323204303926287</v>
+        <v>-0.001332824503567626</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.000110822069192637</v>
+        <v>-0.0009599962734990336</v>
       </c>
       <c r="G6" t="n">
-        <v>8.32102249607558e-05</v>
+        <v>-0.001408041294933549</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0007726447753581833</v>
+        <v>-0.0009124597749568919</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001209579445460632</v>
+        <v>-0.002476302425876253</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0006736777905564706</v>
+        <v>-0.002442136084407246</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0002210407565257783</v>
+        <v>-0.0004275245629088264</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0006192707478413856</v>
+        <v>-9.646082709540983e-05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001486105264976934</v>
+        <v>-0.001395589681087333</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003841002679989014</v>
+        <v>6.35086631178644e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001607316632165839</v>
+        <v>-0.001730679670344673</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0004824530059853865</v>
+        <v>-0.0004605680688002101</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001475943002545468</v>
+        <v>-0.001206580141707575</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0008900740828401449</v>
+        <v>-0.0002580699796323471</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0008662755506965103</v>
+        <v>-0.001915800422874558</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0002475360461981158</v>
+        <v>-0.0006287137996741438</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0005391203327042487</v>
+        <v>-0.0003707352792483826</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0002659311180678164</v>
+        <v>-0.001938491511759563</v>
       </c>
       <c r="W6" t="n">
-        <v>8.643042350911513e-05</v>
+        <v>-0.001735078327338493</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.002645093096075646</v>
+        <v>-0.001362982971941265</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.000665602078700589</v>
+        <v>-0.0002238763707851449</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.001404799833897916</v>
+        <v>-0.0006475248098688103</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.002190434044790843</v>
+        <v>-0.0009459110202485466</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.000176088875165073</v>
+        <v>-0.0003106467540159169</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.001767182993760896</v>
+        <v>-0.002940794193338284</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.003475654154710411</v>
+        <v>0.00170580674684209</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.00385868527704584</v>
+        <v>0.002711101903733851</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0001994091580502122</v>
+        <v>0.0008404532617292486</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0009174579103819581</v>
+        <v>-0.0009167488942945722</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0002575784076290138</v>
+        <v>-0.000645900385000503</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0002414079990248924</v>
+        <v>-0.0003177796503980202</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.000787734341424312</v>
+        <v>-0.0001375305623472045</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.01204558067916968</v>
+        <v>0.003731992577767568</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.001314104307729794</v>
+        <v>-0.001645979521512839</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0007748447868949459</v>
+        <v>-0.001036449041791179</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.0004868177684973385</v>
+        <v>-0.0007146964493645019</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003607805761696092</v>
+        <v>-0.001602473023126333</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0006847350919965744</v>
+        <v>-0.001834160603943238</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.000822544985160592</v>
+        <v>-0.000766722408390938</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.003622496634707895</v>
+        <v>0.003263658333071504</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.0002949381274941654</v>
+        <v>-0.0003187274645869792</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0009082676237875037</v>
+        <v>-0.001753904620478486</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.000552934237688052</v>
+        <v>-0.0007514982682216897</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001011477074382761</v>
+        <v>-0.0008640705178768665</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001444336584514944</v>
+        <v>-0.00191599823918954</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0003734422863059694</v>
+        <v>-0.000438019589872779</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0003443541115424137</v>
+        <v>-0.0006413767247252566</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0004941510042615587</v>
+        <v>-0.0004718067963575462</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.0003181285107476783</v>
+        <v>-0.001375635332138755</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.001310598769199611</v>
+        <v>-0.002241572421517518</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.000385121416541559</v>
+        <v>-0.0005497119162206909</v>
       </c>
       <c r="BD6" t="n">
-        <v>-3.936662097480669e-05</v>
+        <v>-5.167244204909715e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.001547813131551667</v>
+        <v>-0.0007617152485610374</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.0006804328076983806</v>
+        <v>-0.0009973645289364508</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.920663114272473e-05</v>
+        <v>-0.001890084941071216</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0003487948204567937</v>
+        <v>-0.0006430315827197858</v>
       </c>
       <c r="BI6" t="n">
-        <v>-7.338560150770555e-05</v>
+        <v>-0.0004690176127396944</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0006227490478929287</v>
+        <v>-0.0001204155574738935</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.0004142863531076041</v>
+        <v>-0.00231566360838617</v>
       </c>
       <c r="BL6" t="n">
-        <v>-7.886752251694829e-05</v>
+        <v>-0.0003182268814225536</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001331113872571818</v>
+        <v>-0.001185256605666513</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001327747485283193</v>
+        <v>-0.001558398099653644</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001212774549276571</v>
+        <v>-0.0009735064627860557</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001427376445131656</v>
+        <v>-0.001358466974241016</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001762372451606969</v>
+        <v>-0.001068899557599218</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.0009439976613717704</v>
+        <v>-0.001386679707825259</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0009098751826710188</v>
+        <v>0.0004005927963775441</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.00122209338251279</v>
+        <v>-2.160760587724686e-05</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001942283683856669</v>
+        <v>-0.001699357802462403</v>
       </c>
       <c r="BW6" t="n">
-        <v>-2.340093603743765e-05</v>
+        <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.001938241023797987</v>
+        <v>-0.0007926959270460748</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.004021612839515951</v>
+        <v>-0.00168388281986048</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.003198673532609206</v>
+        <v>-0.001127240858668752</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0002881793432656571</v>
+        <v>-0.0003695948962551265</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.001151830038688476</v>
+        <v>-0.001972655684149044</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0009160148506087095</v>
+        <v>-9.559389149871867e-05</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.001468978281894132</v>
+        <v>-0.0005808783077951796</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.001761230273717423</v>
+        <v>-0.002642659729377655</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001011266376234374</v>
+        <v>-0.0007257950847061267</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0008608504521219362</v>
+        <v>0.0001551746974863849</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.00100982098265821</v>
+        <v>-0.001316257356895756</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.002388796975674312</v>
+        <v>-0.002458728049684239</v>
       </c>
       <c r="CJ6" t="n">
         <v>-2.160760587726629e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001264363889922743</v>
+        <v>-0.001536154339822707</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.00164168132010051</v>
+        <v>-0.001267854880649635</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0003998318352579494</v>
+        <v>-0.0002824466490666228</v>
       </c>
       <c r="CN6" t="n">
-        <v>-1.16279769495825e-05</v>
+        <v>0.0003151986899684156</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0002061435124765643</v>
+        <v>-0.0002518552205569596</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.0001393128300979457</v>
+        <v>-6.631299734745355e-05</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0006285654067110791</v>
+        <v>-0.001294209044273087</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.002690854389597619</v>
+        <v>-0.005101340096611525</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.0004518816866508235</v>
+        <v>-0.0003438819975250918</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.001279126784146273</v>
+        <v>-0.003127458806549924</v>
       </c>
       <c r="CU6" t="n">
-        <v>-6.18044850728472e-05</v>
+        <v>-8.108404609190878e-05</v>
       </c>
       <c r="CV6" t="n">
-        <v>3.120124804991964e-05</v>
+        <v>-2.969367428301284e-05</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.001115212329378779</v>
+        <v>-0.001964551725284308</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0004489360850713775</v>
+        <v>-0.003751948810854749</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0003265289949822836</v>
+        <v>-0.0005840990361798664</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0001761937893911436</v>
+        <v>-2.292176039122573e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0.0003755773431770026</v>
+        <v>-0.001782217135412803</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.001897743312089192</v>
+        <v>-0.002182029275843961</v>
       </c>
       <c r="DD6" t="n">
-        <v>-8.186892144854408e-05</v>
+        <v>-0.0001254175039773736</v>
       </c>
       <c r="DE6" t="n">
-        <v>-0.0001919888065662928</v>
+        <v>-0.0005270692393397002</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0008617408442600838</v>
+        <v>-0.002659777122070367</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.001001448493147519</v>
+        <v>-0.0001476081515170508</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.0009851786914277932</v>
+        <v>-0.002496060405709813</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0006699521566760125</v>
+        <v>-0.0009068271314293469</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0004977100920268874</v>
+        <v>-0.0003836443129063116</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.786498520873538e-05</v>
+        <v>-0.001143112864834281</v>
       </c>
       <c r="DL6" t="n">
-        <v>-0.0001920892050692818</v>
+        <v>-2.219591595146453e-05</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0005888069793286016</v>
+        <v>-0.0004487676140249225</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.002728070352721401</v>
+        <v>-0.0017668666140329</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.003280947081287899</v>
+        <v>-0.001934703604780807</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.001711677724739291</v>
+        <v>-0.00149960633968847</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-4.321521175453258e-05</v>
+        <v>-0.0002674733310106536</v>
       </c>
       <c r="DR6" t="n">
-        <v>-5.881004394183709e-05</v>
+        <v>-0.0001184156297275807</v>
       </c>
       <c r="DS6" t="n">
-        <v>-3.087606038845447e-05</v>
+        <v>-9.230714056146227e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.0009018746330681865</v>
+        <v>-0.001835008978222483</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.0002284027439357322</v>
+        <v>-0.002183979763377786</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-5.162026338728642e-05</v>
+        <v>-4.339123695625557e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0007227770001902196</v>
+        <v>-0.0001483940798180761</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.00186457797654585</v>
+        <v>-0.002353015613031229</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-5.091867859711442e-05</v>
+        <v>-7.623106569124014e-06</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0004318810322451711</v>
+        <v>-0.0003622566723988946</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.002761059518047484</v>
+        <v>-0.002148808049185466</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0008005628062495885</v>
+        <v>-0.0009693861487966497</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.000682610341017592</v>
+        <v>-0.0007686158289776312</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-4.439183190292906e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.000303317956113533</v>
+        <v>-0.001033224999302651</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0005286906182367795</v>
+        <v>-0.0004084964012071174</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0001449313912399997</v>
+        <v>3.608224830031759e-17</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001864877466453796</v>
+        <v>-0.0004307856422946232</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.001262743702329774</v>
+        <v>-0.0008296642821350786</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.001225295511396066</v>
+        <v>3.072207240367997e-05</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-2.211736950751553e-05</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0002108137600339566</v>
+        <v>-4.440497335702065e-05</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0001626218985651545</v>
+        <v>-0.0002498269050971752</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0002723663812597033</v>
+        <v>-2.958801105073239e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>5.990380827228803e-05</v>
+        <v>-0.000870210952364528</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-2.935910840911327e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>-2.2202486678502e-05</v>
+        <v>-3.94010431820302e-05</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0007486165002816541</v>
+        <v>-0.0002321695116990735</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.0004846997723700869</v>
+        <v>-0.001277857022700399</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0002340093603743986</v>
+        <v>-8.841732979661399e-05</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0005178131501687972</v>
+        <v>9.891533032075351e-05</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0004378408214116669</v>
+        <v>-0.0002165688876741123</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.000369682540210331</v>
+        <v>-0.0004127549375628065</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0009752588301694619</v>
+        <v>0.0004163967683300518</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000675663868586096</v>
+        <v>0.0003015689730874293</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0003648844806961205</v>
+        <v>-7.371593527553122e-05</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0004911734879517293</v>
+        <v>0.0002300227902764795</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002467349305219468</v>
+        <v>-0.0001304388096652287</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0006942332137139185</v>
+        <v>0.0004642536427712396</v>
       </c>
       <c r="H7" t="n">
-        <v>6.84951852033544e-05</v>
+        <v>-8.593223092830392e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>8.75625504417832e-05</v>
+        <v>0.0009018551191525892</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001916753625611389</v>
+        <v>-0.001939662968159456</v>
       </c>
       <c r="K7" t="n">
-        <v>1.473622163278288e-05</v>
+        <v>-2.042070436885645e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.440507058481644e-05</v>
+        <v>5.872711533423391e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.000412906403896579</v>
+        <v>-0.0005001257521564883</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0005169278148429435</v>
+        <v>0.000738659486241694</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0006057330735993905</v>
+        <v>-0.000619626814894475</v>
       </c>
       <c r="P7" t="n">
-        <v>-8.62375219511713e-05</v>
+        <v>0.0003171695971123933</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.004449270105635733</v>
+        <v>0.002182727207250823</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0003808772304191577</v>
+        <v>0.0004812229798537682</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001325912292059972</v>
+        <v>-1.32095171447133e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004361179895536804</v>
+        <v>-9.885255808977369e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.000113414875299056</v>
+        <v>0.0008840999681025586</v>
       </c>
       <c r="V7" t="n">
-        <v>0.001572320365439645</v>
+        <v>8.493957256002209e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0004107733412621661</v>
+        <v>-0.0009095833934430975</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0008547008547008405</v>
+        <v>6.858335011561401e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.000206385325209002</v>
+        <v>0.0001774546873256067</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0008085138435494743</v>
+        <v>0.0001174610315833102</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002597867067030746</v>
+        <v>0.0006669998181369541</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003114162270763165</v>
+        <v>0.0001959304969169351</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0007343912194839819</v>
+        <v>-0.001050627035396373</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.005542319077750368</v>
+        <v>0.004506337187231329</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.006776512978814026</v>
+        <v>0.004124847054729824</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.002745492635814645</v>
+        <v>0.002059529664529808</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0005552144717896335</v>
+        <v>-0.0005770225749097191</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.000168412359966319</v>
+        <v>-0.0003255663835296463</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0009201292394482973</v>
+        <v>0.0004383588761452229</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.002738887083573271</v>
+        <v>0.001678415142514128</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01439471096980121</v>
+        <v>0.007587632892708434</v>
       </c>
       <c r="AL7" t="n">
-        <v>-0.00054647157646735</v>
+        <v>-0.0009220310953420962</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.00348713122870094</v>
+        <v>0.001236222114679652</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001012147057818769</v>
+        <v>0.0006048119749541114</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.001063855274214015</v>
+        <v>0.0007131337817118943</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0002217231025060329</v>
+        <v>-1.479727730099856e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.000777756952974773</v>
+        <v>0.0005453142586997583</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.009819283667816809</v>
+        <v>0.005193627857510141</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.428819647300799e-05</v>
+        <v>0.0002507943846506711</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.201314298515562e-05</v>
+        <v>0.0006423854676361473</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.001028117887716562</v>
+        <v>-0.0001624035002389834</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0006406650696798744</v>
+        <v>0.0002964637964845473</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0007604396584639406</v>
+        <v>-0.0004110175114916626</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0001187654730595511</v>
+        <v>-0.0002089959151300058</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.0002051754002249439</v>
+        <v>0.001546994252067158</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001934711096309066</v>
+        <v>0.0008458950869613957</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.002249275191990285</v>
+        <v>-0.0009728861344191653</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0002367389148768606</v>
+        <v>-0.0004429478624382143</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0001513025694959036</v>
+        <v>9.139903967478324e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0001033191196269989</v>
+        <v>0.0001592489508349837</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0002412261882771716</v>
+        <v>0.0003537738005216395</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0007201218403044774</v>
+        <v>0.0008648278916836283</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0005735433915729005</v>
+        <v>-0.001088070556534354</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.0001036422135408943</v>
+        <v>-0.0002259450146830655</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.005364550424438929</v>
+        <v>0.001683863851166295</v>
       </c>
       <c r="BJ7" t="n">
-        <v>7.515746901931575e-05</v>
+        <v>0.000976067713766321</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0001464418127287315</v>
+        <v>1.993658341202802e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002065333250279577</v>
+        <v>6.267627702916668e-05</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0001660524101367411</v>
+        <v>-0.0006246746532040937</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0007825800394809012</v>
+        <v>0.0002648434913388176</v>
       </c>
       <c r="BO7" t="n">
-        <v>-4.431314623337123e-05</v>
+        <v>0.0009589681958542707</v>
       </c>
       <c r="BP7" t="n">
-        <v>-2.855633712492422e-05</v>
+        <v>-0.0007740217654682802</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.0003998661168940321</v>
+        <v>-1.783179784251021e-05</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.000576774908981842</v>
+        <v>-0.0007820297327759019</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.853067685928192e-05</v>
+        <v>0.0008822044977662702</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.656889025238641e-05</v>
+        <v>0.0001920236336780123</v>
       </c>
       <c r="BV7" t="n">
-        <v>-9.79359706143601e-06</v>
+        <v>-0.0009383935346127858</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.551115123125783e-18</v>
+        <v>1.477104874447188e-05</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.0006158313748279964</v>
+        <v>-0.0003761736430195062</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.00228883266732266</v>
+        <v>0.0004949097227970767</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.001470341941435144</v>
+        <v>-0.0002795794418540109</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.000381485420238703</v>
+        <v>0.0002483359599117219</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0004947369247241318</v>
+        <v>5.019858742077998e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0003116179434576205</v>
+        <v>0.00040765625025313</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.000708104834830231</v>
+        <v>0.0002045959208575365</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0002513963427775157</v>
+        <v>-0.0009321719058993427</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0005533060156539982</v>
+        <v>-0.0001707658231966225</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0002375720382417013</v>
+        <v>0.0006041115790973494</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0003795216440438509</v>
+        <v>-2.980438305407726e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.000310254377974889</v>
+        <v>0.000635650395985382</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.0001609837737781672</v>
+        <v>-0.0005163946451574198</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0004588205105563793</v>
+        <v>-9.679824845805761e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0008107442395974996</v>
+        <v>0.0003257595435737059</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0007779750697184895</v>
+        <v>0.0006075833472526161</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.001731748676446471</v>
+        <v>0.0003764179665069034</v>
       </c>
       <c r="CP7" t="n">
-        <v>3.885780586188048e-17</v>
+        <v>6.088023600349102e-05</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.001683217695456002</v>
+        <v>0.0005893780371399926</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.000441981489798121</v>
+        <v>-0.0009252805272584098</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0001917100048046405</v>
+        <v>9.071924897847138e-05</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.0006495234242170356</v>
+        <v>-0.0006489910898025031</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0001654116065898603</v>
+        <v>2.912379976288682e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0001957917411483767</v>
+        <v>7.640518764623905e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0004344439009530243</v>
+        <v>-0.001071185385631718</v>
       </c>
       <c r="CY7" t="n">
-        <v>5.260429351893747e-05</v>
+        <v>-0.0009078318819606412</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.110223024625157e-17</v>
+        <v>-0.0002664298401420906</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.00032064981948845</v>
+        <v>0.0002323110201556289</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001498335494306319</v>
+        <v>-0.0003804989653043045</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.0004432101480033979</v>
+        <v>0.0002560852803388469</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.96033155713471e-05</v>
+        <v>4.712132250572209e-05</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0009149892227603373</v>
+        <v>-5.959431982753282e-05</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0003300626407079122</v>
+        <v>-0.0007418343781694148</v>
       </c>
       <c r="DG7" t="n">
-        <v>-4.436541771230539e-05</v>
+        <v>0.0005988886136458038</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.000465517168216828</v>
+        <v>-0.001656683746511645</v>
       </c>
       <c r="DI7" t="n">
-        <v>-2.837239032993486e-07</v>
+        <v>-0.0004599080236784514</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.0001464039461452238</v>
+        <v>0.0002660624772959031</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0002513833100267537</v>
+        <v>-0.0002323419773208324</v>
       </c>
       <c r="DL7" t="n">
-        <v>-6.844523232074493e-08</v>
+        <v>8.896228175800935e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0003395599855641806</v>
+        <v>-7.356353038580065e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.0004064300574058655</v>
+        <v>-0.000684545926190172</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.00103496401205942</v>
+        <v>0.0001037633193708532</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.001169681230945013</v>
+        <v>0.0001941081888253038</v>
       </c>
       <c r="DQ7" t="n">
-        <v>7.436536857197696e-05</v>
+        <v>-1.655897531744887e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>-3.046634655827774e-05</v>
+        <v>1.480165778567355e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-1.477104874446078e-05</v>
       </c>
       <c r="DT7" t="n">
-        <v>-0.0001345985892611368</v>
+        <v>0.0003405425306909959</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0002846152671378443</v>
+        <v>0.0003067133758053619</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002488520719506726</v>
+        <v>0.000251370114220989</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0003541915409937146</v>
+        <v>7.487549342161115e-05</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.0007758694708296653</v>
+        <v>-0.0009904254919091472</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0004005361864332979</v>
+        <v>0.0004776510115057642</v>
       </c>
       <c r="EA7" t="n">
-        <v>-6.18044850728694e-05</v>
+        <v>0.0002386920219882349</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0007623962705300858</v>
+        <v>-0.0009282670821972039</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.0001650787973918266</v>
+        <v>5.586807632080304e-05</v>
       </c>
       <c r="ED7" t="n">
-        <v>-5.728815395220631e-05</v>
+        <v>-0.0001314755260616696</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.48016577856902e-05</v>
+        <v>5.551115123125783e-18</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001410216233155848</v>
+        <v>-0.0003155801467106367</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0002774346077339229</v>
+        <v>-3.024289675743197e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>7.800312012481991e-05</v>
+        <v>3.008283137980184e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.001275753860093948</v>
+        <v>0.0001647056354833365</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0006067540766104884</v>
+        <v>8.950723371936586e-05</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0001344156390850004</v>
+        <v>0.0002748590825285335</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-7.38552437223039e-05</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>1.440507058487195e-05</v>
+        <v>1.457048168895803e-06</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0001020121142423225</v>
+        <v>0.000146429602789655</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.0006119665495962267</v>
+        <v>0.0001991347725321668</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.487209994051053e-05</v>
+        <v>7.487549342163891e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0003636566250663165</v>
+        <v>0.000194840592994211</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0003319764974506645</v>
+        <v>-0.0003899831475195404</v>
       </c>
       <c r="EV7" t="n">
-        <v>5.888428101183396e-05</v>
+        <v>2.96033155713471e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.0002986146478083041</v>
+        <v>0.0003239203769409005</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0001180899827373683</v>
+        <v>0.000517231578385824</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.0003408456842791563</v>
+        <v>-0.0001207317727969115</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000412334913509968</v>
+        <v>0.003003380367145411</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001211867450241316</v>
+        <v>0.0008507127096610196</v>
       </c>
       <c r="D8" t="n">
-        <v>-7.436049970291347e-06</v>
+        <v>0.0001459469404705399</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007183748841396525</v>
+        <v>0.001026682921689606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0005840955915452556</v>
+        <v>0.0008138218622209786</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002204776829072236</v>
+        <v>0.002532338116844115</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001249715378232955</v>
+        <v>0.00127002510840766</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002546328496123884</v>
+        <v>0.001903237298685973</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001609414826630009</v>
+        <v>0.0002046609876366706</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004125869613809924</v>
+        <v>0.0005322654831058843</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003184914728257493</v>
+        <v>0.0003851033230230505</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003402850838644111</v>
+        <v>-7.270717172093433e-05</v>
       </c>
       <c r="N8" t="n">
-        <v>0.004095109633118247</v>
+        <v>0.001657296303491243</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00140654488808801</v>
+        <v>0.001373384289512</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0006438836286842498</v>
+        <v>0.0005798968374064961</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005436053313135058</v>
+        <v>0.008237789628093892</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0008324746273608103</v>
+        <v>0.0006415484546142742</v>
       </c>
       <c r="S8" t="n">
-        <v>0.00205145611248769</v>
+        <v>0.0001856583590050892</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0007884540301200144</v>
+        <v>0.0003265331284667661</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0004383154237276338</v>
+        <v>0.001666894384478792</v>
       </c>
       <c r="V8" t="n">
-        <v>0.004772419382690083</v>
+        <v>0.001113765162028344</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001296811227890118</v>
+        <v>0.0007220467790004043</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003472985677309331</v>
+        <v>0.0009141333207956043</v>
       </c>
       <c r="Y8" t="n">
-        <v>-8.281454853696911e-05</v>
+        <v>0.0004265404447938049</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00338735130222263</v>
+        <v>0.001529957847294367</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005384294758401912</v>
+        <v>0.005281618260483264</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00042596303833142</v>
+        <v>0.0005760567501352038</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001668909688679671</v>
+        <v>2.061415273352241e-05</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.007665510919584622</v>
+        <v>0.009102926538621815</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01340090101537966</v>
+        <v>0.00628000755469702</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.004110993036524335</v>
+        <v>0.002800216728058216</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001005889131706383</v>
+        <v>0.0001475574422385551</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0007182862769567894</v>
+        <v>0.0007654323189480311</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.002386931561885941</v>
+        <v>0.0007231029266492494</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.007464015473998498</v>
+        <v>0.005331827069558359</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.020712980218047</v>
+        <v>0.01713442044111125</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.0002548431633520226</v>
+        <v>-0.0002924757244358811</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.004259957232542088</v>
+        <v>0.00547009509895407</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.0008044221226137711</v>
+        <v>0.001161025491113998</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001090720482884944</v>
+        <v>0.001873818552984321</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001460161946626104</v>
+        <v>0.0002294103911573087</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.003701030810070324</v>
+        <v>0.002322287229064399</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.01320020509460898</v>
+        <v>0.008856886859744072</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0005907205368791719</v>
+        <v>0.0008851714988884457</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001992908006699587</v>
+        <v>0.001845003992558803</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001631768719024662</v>
+        <v>0.0003147050067010354</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0004324747702552145</v>
+        <v>0.001281576136170326</v>
       </c>
       <c r="AW8" t="n">
-        <v>-5.190077299771501e-05</v>
+        <v>-6.482281763179609e-05</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.519426619764509e-05</v>
+        <v>0.0008625720359408867</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.0004718894876392904</v>
+        <v>0.00316356970442232</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.004022522281472077</v>
+        <v>0.002096900052091985</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004494834965812447</v>
+        <v>0.001643795975596585</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.002124222047533616</v>
+        <v>0.002965987303814574</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0002509121433423384</v>
+        <v>0.0004284403312731694</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0002432521382758595</v>
+        <v>0.000417940423527885</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.002958007975491464</v>
+        <v>0.002478760479211911</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002285137539917131</v>
+        <v>0.004813428399173902</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001188557922554498</v>
+        <v>0.0006067544796512697</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0006808088415490937</v>
+        <v>0.0007265735226045123</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.007169520751372175</v>
+        <v>0.00917846705486162</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0009258327052621002</v>
+        <v>0.0028064505484733</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.000862559736664012</v>
+        <v>0.001656185183113537</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.000470925590047852</v>
+        <v>0.0002640925319164378</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0007416566325574636</v>
+        <v>0.0003867756496493235</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.002676946814632189</v>
+        <v>0.001845191166803645</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001867697527329182</v>
+        <v>0.001683531827365914</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0009360305458736063</v>
+        <v>0.001039581753493041</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.001559349474552757</v>
+        <v>0.001766189973508167</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002042633429475138</v>
+        <v>-7.615427341751968e-05</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.000820298762028568</v>
+        <v>0.002210623256390942</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0008563418589567273</v>
+        <v>0.00180891910260699</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.0007656509674596441</v>
+        <v>0.0003021535991401009</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.916288064738984e-05</v>
+        <v>3.093965385618236e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0006867772995390626</v>
+        <v>0.0003096562101636669</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0005303472567772666</v>
+        <v>0.001701563160007463</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.0002617116178900453</v>
+        <v>0.001367120084713436</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.001456642745135239</v>
+        <v>0.001232818001523645</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001853875489514736</v>
+        <v>0.001075638786524311</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001730602320529809</v>
+        <v>0.001555909546895326</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.001123450265494197</v>
+        <v>0.0007164148634911299</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001239646292108915</v>
+        <v>-0.0004239172826386306</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0004059584508106229</v>
+        <v>0.0006510277441299283</v>
       </c>
       <c r="CG8" t="n">
-        <v>4.436538690092695e-05</v>
+        <v>0.001011832026942497</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0006626117334206178</v>
+        <v>0.0005596512122063579</v>
       </c>
       <c r="CI8" t="n">
-        <v>6.271049964529096e-05</v>
+        <v>0.001070573023101529</v>
       </c>
       <c r="CJ8" t="n">
-        <v>5.176428840543423e-05</v>
+        <v>2.952902961919912e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0005567849372777378</v>
+        <v>0.000739283923044337</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0008524915125097843</v>
+        <v>0.0004022155001303762</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001930397109312476</v>
+        <v>0.001268687570822283</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001057173398999853</v>
+        <v>0.0009686579149738583</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002416473248172013</v>
+        <v>0.0007239077651397612</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.000117907186618052</v>
+        <v>0.0004479165578109373</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001905454415477242</v>
+        <v>0.001924760205052864</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002125734077466207</v>
+        <v>0.000380911263345371</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0003196005034419274</v>
+        <v>0.0005295105256361149</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0003274579553067536</v>
+        <v>0.0005042787286063332</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0003060931426021623</v>
+        <v>0.0001998192287242379</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003467324347404321</v>
+        <v>0.0001780148165680034</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0002455181992786243</v>
+        <v>0.0001025735225815172</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.00146240154138966</v>
+        <v>0.0007715053186720471</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002892908601675404</v>
+        <v>0.0001550960118168382</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0004939420415914414</v>
+        <v>0.0004421387972166846</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002464527408380687</v>
+        <v>0.0007216511311952695</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0005198793526313417</v>
+        <v>0.001201315528102567</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0003582382586293204</v>
+        <v>0.0004398492001016635</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.001904341342193072</v>
+        <v>0.0001747568450268327</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0004011476958530657</v>
+        <v>0.0008893237999237497</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0009148312412989191</v>
+        <v>0.0009838410350454187</v>
       </c>
       <c r="DH8" t="n">
-        <v>-0.0003681931619952949</v>
+        <v>0.0007021581940037408</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0002632311055789483</v>
+        <v>-0.0001804448390527846</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.002035881435257403</v>
+        <v>0.0013570826150511</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0005448770160967869</v>
+        <v>0.0003379435506447537</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0001844249021239669</v>
+        <v>0.0002000337065710983</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0007321263580914034</v>
+        <v>0.0003100744128061689</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0006556268149685796</v>
+        <v>0.0003613685810509165</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.0005306876602984928</v>
+        <v>0.001548585440473499</v>
       </c>
       <c r="DP8" t="n">
-        <v>-0.000632954619344278</v>
+        <v>0.001526550059557413</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0002620830591700707</v>
+        <v>0.0001853347695489532</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.420866489834863e-05</v>
+        <v>0.0001317409018200072</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>5.201493847201977e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001003680402991705</v>
+        <v>0.0008913507120806297</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.00059493367071414</v>
+        <v>0.00160738275912129</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0003538776798442722</v>
+        <v>0.0007024237324550625</v>
       </c>
       <c r="DX8" t="n">
-        <v>3.002596850038286e-05</v>
+        <v>0.0006283958399458834</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001046336388167501</v>
+        <v>-7.225634214199362e-05</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0007712936912681795</v>
+        <v>0.0008840980209467164</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0001491300730587536</v>
+        <v>0.0009588733035711672</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0004718022991414078</v>
+        <v>0.001317543329973478</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0004949414136990349</v>
+        <v>0.001248289480310028</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0003246238517893047</v>
+        <v>0.0002683902770551694</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001410305755638525</v>
+        <v>7.020280811234347e-05</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0007765763307218593</v>
+        <v>-4.51242470697083e-05</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.000474159882200345</v>
+        <v>0.0002572385255377896</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002289913058519277</v>
+        <v>0.0001428788880683901</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0001993307508318637</v>
+        <v>0.0008204620319644529</v>
       </c>
       <c r="EJ8" t="n">
-        <v>4.77602233674046e-05</v>
+        <v>0.0002004701956087179</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0006392468169475196</v>
+        <v>0.001135934308641631</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>0</v>
+        <v>1.942890293094024e-17</v>
       </c>
       <c r="EN8" t="n">
-        <v>5.171397512621912e-05</v>
+        <v>0.0001404520230228745</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0005179445329372174</v>
+        <v>0.0002650165425527984</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0009363044448428559</v>
+        <v>0.0005538881397042367</v>
       </c>
       <c r="ER8" t="n">
-        <v>4.440497335702065e-05</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0001794756215194066</v>
+        <v>0.0002024554016201413</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0.0001351173896961377</v>
+        <v>0.0006464816170299841</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0003233155649320446</v>
+        <v>5.742198873900651e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0001921001562810193</v>
+        <v>0.0002302556698395436</v>
       </c>
       <c r="EW8" t="n">
-        <v>-0.0001799773677836958</v>
+        <v>0.0008382372403740818</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.000251569045813016</v>
+        <v>0.001085788799124254</v>
       </c>
       <c r="EY8" t="n">
-        <v>-2.211736950755993e-05</v>
+        <v>0.0004442721107376979</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00371802498512791</v>
+        <v>0.005562165377751305</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001528861154446204</v>
+        <v>0.00566204659392514</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0004056162246490303</v>
+        <v>0.00251628182356427</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001709401709401759</v>
+        <v>0.004055654233274153</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009714822939516976</v>
+        <v>0.001716484166913257</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01124925991711075</v>
+        <v>0.009377764671188494</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002776911076443056</v>
+        <v>0.004450338933097609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.009577632361689481</v>
+        <v>0.003907637655417406</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005621653777513369</v>
+        <v>0.0007990529742527231</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00142095914742455</v>
+        <v>0.001344743276283555</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000769686204854958</v>
+        <v>0.0005473926822241792</v>
       </c>
       <c r="M9" t="n">
-        <v>0.001119952844090799</v>
+        <v>0.002101213376738675</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01769779892920881</v>
+        <v>0.01177870315288514</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004580606781677587</v>
+        <v>0.001872074882995311</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00254588513913564</v>
+        <v>0.007991742848717232</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01600237953599047</v>
+        <v>0.01900654372397376</v>
       </c>
       <c r="R9" t="n">
-        <v>0.004640095181439619</v>
+        <v>0.00359775877322327</v>
       </c>
       <c r="S9" t="n">
-        <v>0.005116002379535978</v>
+        <v>0.002885187388459187</v>
       </c>
       <c r="T9" t="n">
-        <v>0.003033908387864393</v>
+        <v>0.001754935756816023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003868954758190368</v>
+        <v>0.00262459451489242</v>
       </c>
       <c r="V9" t="n">
-        <v>0.008461297398934465</v>
+        <v>0.003243880861102966</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0015039811265113</v>
+        <v>0.002888299440023623</v>
       </c>
       <c r="X9" t="n">
-        <v>0.005734879348166688</v>
+        <v>0.005860231902224988</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001070791195716836</v>
+        <v>0.001208370173887474</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.004570923031554042</v>
+        <v>0.003463587921847267</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.01365258774538964</v>
+        <v>0.01049218980253466</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001532567049808453</v>
+        <v>0.00106549670949545</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00500296033155716</v>
+        <v>0.002169926650366705</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01088637715645449</v>
+        <v>0.01072796934865905</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02123735871505056</v>
+        <v>0.01969066032123732</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.005532421177870306</v>
+        <v>0.003896490184413981</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.002944675788221329</v>
+        <v>0.001592450604541473</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001576442593694227</v>
+        <v>0.0015039811265114</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.007252812314979329</v>
+        <v>0.002122015915119413</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.02085068411659727</v>
+        <v>0.01041046995835807</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.04600355239786859</v>
+        <v>0.02015915119363402</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001061007957559723</v>
+        <v>0.001033973412112255</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.01032123735871505</v>
+        <v>0.01273051754907788</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.003772472737990018</v>
+        <v>0.002528256989886923</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002527301092043699</v>
+        <v>0.004888749608273258</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002322738386308099</v>
+        <v>0.001679929266136215</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.007946210268948706</v>
+        <v>0.0135336109458655</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.02303353180821054</v>
+        <v>0.01604246534945447</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00233866193013621</v>
+        <v>0.001916838690651768</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.003065134099616884</v>
+        <v>0.002536125036862335</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.003049141503848474</v>
+        <v>0.003507220748600104</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00163593099345628</v>
+        <v>0.003137022787807065</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002160402485942548</v>
+        <v>0.002004126142057216</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002139364303178515</v>
+        <v>0.001119952844090821</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.004640095181439619</v>
+        <v>0.006870910172516309</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.006722189173111248</v>
+        <v>0.002456348031962097</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.02278405710886379</v>
+        <v>0.006424318395487317</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008022563459730448</v>
+        <v>0.006811421772754245</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0004992199687987919</v>
+        <v>0.0006216696269982447</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005304212168486977</v>
+        <v>0.001591511936339573</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.006424318395487283</v>
+        <v>0.003063652587745325</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.005599764220453896</v>
+        <v>0.008075449454759853</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.002558001189768011</v>
+        <v>0.002269378131447142</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.001450133175495683</v>
+        <v>0.003743000294724486</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02088042831647829</v>
+        <v>0.01499107674003565</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.004499703966844337</v>
+        <v>0.005861456483126137</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.002064287820701816</v>
+        <v>0.003876886652855904</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.002871521610420424</v>
+        <v>0.001004431314623333</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002498512790005936</v>
+        <v>0.001035809411068345</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.009190957763236163</v>
+        <v>0.007662835249042188</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.01873884592504464</v>
+        <v>0.007525282569898828</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001124593074874203</v>
+        <v>0.001213376738680061</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.005150976909413896</v>
+        <v>0.004418677530554671</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.003123140987507467</v>
+        <v>0.001039119804400945</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002713063992922393</v>
+        <v>0.004804008252284153</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.004144464179988194</v>
+        <v>0.0062462819750148</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002960331557134444</v>
+        <v>0.001069682151589213</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0003848431024275234</v>
+        <v>6.240249609985593e-05</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.004884547069271783</v>
+        <v>0.001894865525672329</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.007882212968471136</v>
+        <v>0.004335004423473931</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.01029149315883402</v>
+        <v>0.003042836041358921</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002901124925991749</v>
+        <v>0.003804187555293448</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.002812314979277708</v>
+        <v>0.00270672218917305</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.003525741029641205</v>
+        <v>0.007225007372456571</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002078239608801979</v>
+        <v>0.003538779121203228</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.004828850855745748</v>
+        <v>0.001657295057709351</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.004865821291654315</v>
+        <v>0.002534630120837056</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.00355239786856133</v>
+        <v>0.006664700678266034</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002022605591909588</v>
+        <v>0.002182247124741998</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002536674816625939</v>
+        <v>0.002101213376738653</v>
       </c>
       <c r="CJ9" t="n">
-        <v>9.36037441497728e-05</v>
+        <v>3.120124804992796e-05</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003777513384889952</v>
+        <v>0.002093777646711959</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.002139364303178526</v>
+        <v>0.001354076634975532</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.003926234384295057</v>
+        <v>0.003108348134991146</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.002260559190957778</v>
+        <v>0.002241226776762084</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003331350386674603</v>
+        <v>0.00491415038484313</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0007077558242405968</v>
+        <v>0.000740082889283622</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.004074955383700185</v>
+        <v>0.00870337477797516</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.01067816775728734</v>
+        <v>0.00336109458655558</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.000468018720748864</v>
+        <v>0.002349791790600786</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.002506112469437682</v>
+        <v>0.003625110521662311</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.001124925991711101</v>
+        <v>0.0007207771858351419</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0008878366380585812</v>
+        <v>0.0006782659982306427</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.001497659906396287</v>
+        <v>0.001130806845965726</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.007108863771564555</v>
+        <v>0.00203359858532276</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0008288928359976522</v>
+        <v>0.001185647425897052</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.00136823319452708</v>
+        <v>0.0009984399375975394</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.004056162246489881</v>
+        <v>0.003197158081705176</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.004045211183819175</v>
+        <v>0.001814396192742351</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0005010315355143402</v>
+        <v>0.000501327042170463</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.003450327186198687</v>
+        <v>0.01093427645151789</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.00306365258774538</v>
+        <v>0.002180960801650511</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.001692259479786873</v>
+        <v>0.008576480990274148</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.001497555012224983</v>
+        <v>0.002308375258952344</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.004804008252284142</v>
+        <v>0.002231051344743218</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.00357579462102694</v>
+        <v>0.00271146478043035</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001934477379095179</v>
+        <v>0.0006418092909534878</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0005806845965770746</v>
+        <v>0.0007667354762607159</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.004292480757844918</v>
+        <v>0.0009769094138543876</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.003728606356968245</v>
+        <v>0.002558502340093616</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.001872074882995345</v>
+        <v>0.002270716602772083</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.002033598585322738</v>
+        <v>0.002881014116969194</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0004736530491415425</v>
+        <v>0.0003169115528666389</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0005501222493887847</v>
+        <v>0.0004584352078239262</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0004144464179988483</v>
+        <v>0.0008552049542907891</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.00271146478043034</v>
+        <v>0.002122015915119413</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.001279251170046825</v>
+        <v>0.002189570728896595</v>
       </c>
       <c r="DV9" t="n">
+        <v>5.897965202006361e-05</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.001894612196566048</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.001555747623163395</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.0006510802012429595</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0015039811265114</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.002433697347893915</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0.001595273264401764</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>0.002740937223695905</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.000710479573712286</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0002082093991671363</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>0.001183782184078108</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>0.001150103214391074</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.001061633736360978</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.001238572692421158</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>0.0002496099843994126</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.002072232089994119</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>0.0001181683899556862</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>3.133813851456946e-05</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.000383367738130358</v>
+      </c>
+      <c r="EO9" t="n">
         <v>0</v>
       </c>
-      <c r="DW9" t="n">
-        <v>0.0009672386895476226</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>0.001065496709495428</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>0.005592909535452373</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.001450562462995886</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>0.002693901716992342</v>
-      </c>
-      <c r="EB9" t="n">
-        <v>0.001699798329011892</v>
-      </c>
-      <c r="EC9" t="n">
-        <v>0.001191931540342339</v>
-      </c>
-      <c r="ED9" t="n">
-        <v>0.001279251170046847</v>
-      </c>
-      <c r="EE9" t="n">
-        <v>0.0004033419763757373</v>
-      </c>
-      <c r="EF9" t="n">
-        <v>0.001622464898595977</v>
-      </c>
-      <c r="EG9" t="n">
-        <v>0.002647233789411074</v>
-      </c>
-      <c r="EH9" t="n">
-        <v>0.0003457216940363383</v>
-      </c>
-      <c r="EI9" t="n">
-        <v>0.0005353955978584346</v>
-      </c>
-      <c r="EJ9" t="n">
-        <v>0.000678265998230565</v>
-      </c>
-      <c r="EK9" t="n">
-        <v>0.001983422143280078</v>
-      </c>
-      <c r="EL9" t="n">
-        <v>5.948839976204212e-05</v>
-      </c>
-      <c r="EM9" t="n">
-        <v>0.0002652519893899585</v>
-      </c>
-      <c r="EN9" t="n">
-        <v>0.0002193669696019751</v>
-      </c>
-      <c r="EO9" t="n">
-        <v>0.0002592912705272954</v>
-      </c>
       <c r="EP9" t="n">
-        <v>0.001397977394408101</v>
+        <v>0.0004992199687987809</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001332149200710497</v>
+        <v>0.001065496709495439</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001784651992861264</v>
+        <v>0.0001253525540582778</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0009168704156479413</v>
+        <v>0.0004718372161604423</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001598579040852621</v>
+        <v>0.001598245064243164</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.003718024985127921</v>
+        <v>0.0009815585960737173</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0005622965374371014</v>
+        <v>0.0004033419763757262</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0009401441554371282</v>
+        <v>0.002871521610420391</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.001747269890795677</v>
+        <v>0.002418165732822242</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0002184087363494847</v>
+        <v>0.001095322676139754</v>
       </c>
     </row>
   </sheetData>
